--- a/Outputs/Scenarios/PtX_demand_HR_Ammonia.xlsx
+++ b/Outputs/Scenarios/PtX_demand_HR_Ammonia.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.0006628818471006026</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0007148512001163051</v>
+        <v>0.0008147123759139894</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.0001568124957807028</v>
       </c>
     </row>
     <row r="18">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00142970240023261</v>
+        <v>0.001254499966245622</v>
       </c>
     </row>
     <row r="20">
@@ -1481,7 +1481,7 @@
         <v>9.55100534594075e-06</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0002382837333721018</v>
+        <v>0.0001568124957807028</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.000981315871154448</v>
       </c>
       <c r="K30" t="n">
-        <v>0.003844949908377436</v>
+        <v>0.004382070386976756</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>0.0008434429307614694</v>
       </c>
     </row>
     <row r="32">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.007689899816754871</v>
+        <v>0.006747543446091755</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>5.164820374497096e-05</v>
       </c>
       <c r="K42" t="n">
-        <v>0.001281649969459145</v>
+        <v>0.0008434429307614694</v>
       </c>
     </row>
     <row r="43">
